--- a/template/daily-work-report-template.xlsx
+++ b/template/daily-work-report-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\00GECMain\Y_Drive\217\50217298 - Pavement Marking - 439\Construction Phase\Daily Work Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jsona\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D9B025C-E63A-4698-A141-812CE1A89EB7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{870540A9-92DC-4C1A-BDF0-8FB2E700EDD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18530" windowHeight="10070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Daily Work Report" sheetId="1" r:id="rId1"/>
@@ -20,17 +20,28 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Daily Work Report'!$A$1:$Q$41</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Daily_Photo_Log!$A$1:$M$61</definedName>
   </definedNames>
-  <calcPr calcId="191028" iterate="1" iterateCount="1" iterateDelta="0"/>
+  <calcPr calcId="191029" iterate="1" iterateCount="1" iterateDelta="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="59">
   <si>
     <t>REPORT NO.</t>
   </si>
@@ -57,9 +68,6 @@
   </si>
   <si>
     <t>PROJECT ENGINEER:</t>
-  </si>
-  <si>
-    <t>Elizabeth Guiza</t>
   </si>
   <si>
     <t>CONTRACTORS FORCE &amp; EQUIP</t>
@@ -206,9 +214,6 @@
     <t>Traffic Control</t>
   </si>
   <si>
-    <t>G.E.C., INC.</t>
-  </si>
-  <si>
     <t>Pickup truck</t>
   </si>
   <si>
@@ -236,22 +241,10 @@
     <t>PE NAME:</t>
   </si>
   <si>
-    <t>JOHN SONNIER</t>
-  </si>
-  <si>
-    <t>439</t>
-  </si>
-  <si>
-    <t>PAVEMENT MARKING OF BRIDGE DECK AND ROADWAY</t>
-  </si>
-  <si>
-    <t>HIGHWAY GRAPHICS</t>
-  </si>
-  <si>
-    <t>Causeway PD</t>
-  </si>
-  <si>
     <t xml:space="preserve">WORK SUMMARY: </t>
+  </si>
+  <si>
+    <t>LOGO</t>
   </si>
 </sst>
 </file>
@@ -1147,9 +1140,9 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="28" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1166,7 +1159,7 @@
     <xf numFmtId="1" fontId="27" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="6" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1196,104 +1189,52 @@
     <xf numFmtId="14" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
@@ -1361,43 +1302,95 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="165" fontId="17" fillId="0" borderId="20" xfId="2" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="1" applyBorder="1" applyAlignment="1">
@@ -1453,9 +1446,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1493,9 +1486,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1528,26 +1521,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1580,26 +1556,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1777,78 +1736,77 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AL45"/>
-  <sheetFormatPr defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="9.81640625" customWidth="1"/>
-    <col min="2" max="2" width="24.7265625" customWidth="1"/>
-    <col min="3" max="3" width="5.26953125" style="11" customWidth="1"/>
-    <col min="4" max="8" width="5.26953125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="9.1796875" customWidth="1"/>
-    <col min="10" max="10" width="9.7265625" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" customWidth="1"/>
+    <col min="2" max="2" width="24.77734375" customWidth="1"/>
+    <col min="3" max="3" width="5.21875" style="11" customWidth="1"/>
+    <col min="4" max="8" width="5.21875" style="4" customWidth="1"/>
+    <col min="9" max="9" width="9.21875" customWidth="1"/>
+    <col min="10" max="10" width="9.77734375" customWidth="1"/>
     <col min="11" max="11" width="4" customWidth="1"/>
-    <col min="12" max="12" width="9.1796875" customWidth="1"/>
-    <col min="13" max="14" width="9.54296875" customWidth="1"/>
-    <col min="15" max="15" width="14.453125" style="14" customWidth="1"/>
-    <col min="16" max="16" width="12.1796875" customWidth="1"/>
-    <col min="17" max="17" width="12.26953125" customWidth="1"/>
+    <col min="12" max="12" width="9.21875" customWidth="1"/>
+    <col min="13" max="14" width="9.5546875" customWidth="1"/>
+    <col min="15" max="15" width="14.44140625" style="14" customWidth="1"/>
+    <col min="16" max="17" width="12.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="12.75" customHeight="1">
-      <c r="A1" s="134"/>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="134"/>
-      <c r="M1" s="134"/>
-      <c r="N1" s="134"/>
-      <c r="O1" s="134"/>
-      <c r="P1" s="134"/>
-      <c r="Q1" s="134"/>
+      <c r="A1" s="118"/>
+      <c r="B1" s="118"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="118"/>
+      <c r="G1" s="118"/>
+      <c r="H1" s="118"/>
+      <c r="I1" s="118"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
     </row>
     <row r="2" spans="1:38" ht="18.75" customHeight="1">
-      <c r="A2" s="134"/>
-      <c r="B2" s="134"/>
-      <c r="C2" s="134"/>
-      <c r="D2" s="134"/>
-      <c r="E2" s="134"/>
-      <c r="F2" s="134"/>
-      <c r="G2" s="134"/>
-      <c r="H2" s="134"/>
-      <c r="I2" s="134"/>
-      <c r="J2" s="134"/>
-      <c r="K2" s="134"/>
-      <c r="L2" s="134"/>
-      <c r="M2" s="134"/>
-      <c r="N2" s="134"/>
-      <c r="O2" s="134"/>
-      <c r="P2" s="134"/>
-      <c r="Q2" s="134"/>
-    </row>
-    <row r="3" spans="1:38" ht="18">
+      <c r="A2" s="118"/>
+      <c r="B2" s="118"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
+      <c r="N2" s="118"/>
+      <c r="O2" s="118"/>
+      <c r="P2" s="118"/>
+      <c r="Q2" s="118"/>
+    </row>
+    <row r="3" spans="1:38" ht="17.399999999999999">
       <c r="B3" s="82" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" s="135" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" s="135"/>
-      <c r="E3" s="135"/>
-      <c r="F3" s="135"/>
-      <c r="G3" s="135"/>
-      <c r="H3" s="135"/>
-      <c r="I3" s="135"/>
-      <c r="J3" s="135"/>
-      <c r="K3" s="135"/>
-      <c r="L3" s="135"/>
-      <c r="M3" s="135"/>
-      <c r="N3" s="135"/>
+        <v>58</v>
+      </c>
+      <c r="C3" s="119" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="119"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="119"/>
+      <c r="G3" s="119"/>
+      <c r="H3" s="119"/>
+      <c r="I3" s="119"/>
+      <c r="J3" s="119"/>
+      <c r="K3" s="119"/>
+      <c r="L3" s="119"/>
+      <c r="M3" s="119"/>
+      <c r="N3" s="119"/>
       <c r="P3" s="9" t="s">
         <v>0</v>
       </c>
@@ -1886,33 +1844,25 @@
       <c r="AL4"/>
     </row>
     <row r="5" spans="1:38" s="9" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="128" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="146" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" s="124" t="s">
-        <v>62</v>
-      </c>
-      <c r="D5" s="118" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" s="127"/>
-      <c r="F5" s="118"/>
-      <c r="G5" s="118"/>
-      <c r="H5" s="121"/>
-      <c r="I5" s="136" t="s">
+      <c r="B5" s="130"/>
+      <c r="C5" s="140"/>
+      <c r="D5" s="134"/>
+      <c r="E5" s="143"/>
+      <c r="F5" s="134"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="137"/>
+      <c r="I5" s="120" t="s">
         <v>2</v>
       </c>
-      <c r="J5" s="136"/>
-      <c r="K5" s="137" t="s">
-        <v>59</v>
-      </c>
-      <c r="L5" s="137"/>
-      <c r="M5" s="137"/>
-      <c r="N5" s="137"/>
-      <c r="O5" s="137"/>
+      <c r="J5" s="120"/>
+      <c r="K5" s="121"/>
+      <c r="L5" s="121"/>
+      <c r="M5" s="121"/>
+      <c r="N5" s="121"/>
+      <c r="O5" s="121"/>
       <c r="P5" s="44" t="s">
         <v>3</v>
       </c>
@@ -1939,23 +1889,23 @@
       <c r="AL5"/>
     </row>
     <row r="6" spans="1:38" s="9" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A6" s="145"/>
-      <c r="B6" s="147"/>
-      <c r="C6" s="125"/>
-      <c r="D6" s="119"/>
-      <c r="E6" s="128"/>
-      <c r="F6" s="119"/>
-      <c r="G6" s="119"/>
-      <c r="H6" s="122"/>
-      <c r="I6" s="130" t="s">
+      <c r="A6" s="129"/>
+      <c r="B6" s="131"/>
+      <c r="C6" s="141"/>
+      <c r="D6" s="135"/>
+      <c r="E6" s="144"/>
+      <c r="F6" s="135"/>
+      <c r="G6" s="135"/>
+      <c r="H6" s="138"/>
+      <c r="I6" s="114" t="s">
         <v>4</v>
       </c>
-      <c r="J6" s="130"/>
-      <c r="K6" s="131"/>
-      <c r="L6" s="131"/>
-      <c r="M6" s="131"/>
-      <c r="N6" s="131"/>
-      <c r="O6" s="131"/>
+      <c r="J6" s="114"/>
+      <c r="K6" s="115"/>
+      <c r="L6" s="115"/>
+      <c r="M6" s="115"/>
+      <c r="N6" s="115"/>
+      <c r="O6" s="115"/>
       <c r="P6" s="45"/>
       <c r="Q6" s="74"/>
       <c r="R6" s="49"/>
@@ -1981,33 +1931,29 @@
       <c r="AL6"/>
     </row>
     <row r="7" spans="1:38" s="9" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A7" s="140" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7" s="142" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" s="125"/>
-      <c r="D7" s="119"/>
-      <c r="E7" s="128"/>
-      <c r="F7" s="119"/>
-      <c r="G7" s="119"/>
-      <c r="H7" s="122"/>
-      <c r="I7" s="138" t="s">
+      <c r="A7" s="124" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="126"/>
+      <c r="C7" s="141"/>
+      <c r="D7" s="135"/>
+      <c r="E7" s="144"/>
+      <c r="F7" s="135"/>
+      <c r="G7" s="135"/>
+      <c r="H7" s="138"/>
+      <c r="I7" s="122" t="s">
         <v>5</v>
       </c>
-      <c r="J7" s="138"/>
-      <c r="K7" s="132"/>
-      <c r="L7" s="132"/>
-      <c r="M7" s="132"/>
-      <c r="N7" s="132"/>
-      <c r="O7" s="132"/>
+      <c r="J7" s="122"/>
+      <c r="K7" s="116"/>
+      <c r="L7" s="116"/>
+      <c r="M7" s="116"/>
+      <c r="N7" s="116"/>
+      <c r="O7" s="116"/>
       <c r="P7" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="Q7" s="96">
-        <v>46164</v>
-      </c>
+      <c r="Q7" s="96"/>
       <c r="S7"/>
       <c r="T7"/>
       <c r="U7"/>
@@ -2030,18 +1976,18 @@
       <c r="AL7"/>
     </row>
     <row r="8" spans="1:38" s="9" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A8" s="141"/>
-      <c r="B8" s="143"/>
-      <c r="C8" s="125"/>
-      <c r="D8" s="119"/>
-      <c r="E8" s="128"/>
-      <c r="F8" s="119"/>
-      <c r="G8" s="119"/>
-      <c r="H8" s="122"/>
-      <c r="I8" s="139" t="s">
+      <c r="A8" s="125"/>
+      <c r="B8" s="127"/>
+      <c r="C8" s="141"/>
+      <c r="D8" s="135"/>
+      <c r="E8" s="144"/>
+      <c r="F8" s="135"/>
+      <c r="G8" s="135"/>
+      <c r="H8" s="138"/>
+      <c r="I8" s="123" t="s">
         <v>7</v>
       </c>
-      <c r="J8" s="139"/>
+      <c r="J8" s="123"/>
       <c r="K8" s="20"/>
       <c r="L8" s="20"/>
       <c r="M8" s="20"/>
@@ -2071,29 +2017,27 @@
       <c r="AL8"/>
     </row>
     <row r="9" spans="1:38" s="9" customFormat="1" ht="18" customHeight="1">
-      <c r="A9" s="148" t="s">
-        <v>58</v>
-      </c>
-      <c r="B9" s="97"/>
-      <c r="C9" s="125"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="128"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="119"/>
-      <c r="H9" s="122"/>
-      <c r="I9" s="139"/>
-      <c r="J9" s="139"/>
+      <c r="A9" s="132" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="148"/>
+      <c r="C9" s="141"/>
+      <c r="D9" s="135"/>
+      <c r="E9" s="144"/>
+      <c r="F9" s="135"/>
+      <c r="G9" s="135"/>
+      <c r="H9" s="138"/>
+      <c r="I9" s="123"/>
+      <c r="J9" s="123"/>
       <c r="K9" s="19"/>
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>
       <c r="N9" s="19"/>
       <c r="O9" s="19"/>
       <c r="P9" s="75" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q9" s="10">
-        <f>Q5-Q7+1</f>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="Q9" s="10"/>
       <c r="S9"/>
       <c r="T9"/>
       <c r="U9"/>
@@ -2116,16 +2060,16 @@
       <c r="AL9"/>
     </row>
     <row r="10" spans="1:38" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="A10" s="149"/>
-      <c r="B10" s="98"/>
-      <c r="C10" s="125"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="128"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="119"/>
-      <c r="H10" s="122"/>
-      <c r="I10" s="133"/>
-      <c r="J10" s="133"/>
+      <c r="A10" s="133"/>
+      <c r="B10" s="149"/>
+      <c r="C10" s="141"/>
+      <c r="D10" s="135"/>
+      <c r="E10" s="144"/>
+      <c r="F10" s="135"/>
+      <c r="G10" s="135"/>
+      <c r="H10" s="138"/>
+      <c r="I10" s="117"/>
+      <c r="J10" s="117"/>
       <c r="K10" s="43"/>
       <c r="L10" s="43"/>
       <c r="M10" s="43"/>
@@ -2155,18 +2099,18 @@
       <c r="AL10"/>
     </row>
     <row r="11" spans="1:38" s="1" customFormat="1" ht="15" customHeight="1" thickTop="1">
-      <c r="A11" s="116" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="117"/>
-      <c r="C11" s="126"/>
-      <c r="D11" s="120"/>
-      <c r="E11" s="129"/>
-      <c r="F11" s="120"/>
-      <c r="G11" s="120"/>
-      <c r="H11" s="123"/>
+      <c r="A11" s="146" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="147"/>
+      <c r="C11" s="142"/>
+      <c r="D11" s="136"/>
+      <c r="E11" s="145"/>
+      <c r="F11" s="136"/>
+      <c r="G11" s="136"/>
+      <c r="H11" s="139"/>
       <c r="I11" s="81" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="J11" s="79"/>
       <c r="K11" s="79"/>
@@ -2198,27 +2142,27 @@
       <c r="AL11"/>
     </row>
     <row r="12" spans="1:38" s="1" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A12" s="112" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="113"/>
+      <c r="A12" s="100" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="101"/>
       <c r="C12" s="83"/>
       <c r="D12" s="85"/>
       <c r="E12" s="87"/>
       <c r="F12" s="21"/>
       <c r="G12" s="21"/>
       <c r="H12" s="41"/>
-      <c r="I12" s="99" t="s">
-        <v>48</v>
-      </c>
-      <c r="J12" s="100"/>
-      <c r="K12" s="100"/>
-      <c r="L12" s="100"/>
-      <c r="M12" s="100"/>
-      <c r="N12" s="100"/>
-      <c r="O12" s="100"/>
-      <c r="P12" s="100"/>
-      <c r="Q12" s="101"/>
+      <c r="I12" s="150" t="s">
+        <v>47</v>
+      </c>
+      <c r="J12" s="151"/>
+      <c r="K12" s="151"/>
+      <c r="L12" s="151"/>
+      <c r="M12" s="151"/>
+      <c r="N12" s="151"/>
+      <c r="O12" s="151"/>
+      <c r="P12" s="151"/>
+      <c r="Q12" s="152"/>
       <c r="S12"/>
       <c r="T12"/>
       <c r="U12"/>
@@ -2241,10 +2185,10 @@
       <c r="AL12"/>
     </row>
     <row r="13" spans="1:38" s="1" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A13" s="112" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="113"/>
+      <c r="A13" s="100" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="101"/>
       <c r="C13" s="83"/>
       <c r="D13" s="85"/>
       <c r="E13" s="87"/>
@@ -2282,25 +2226,25 @@
       <c r="AL13"/>
     </row>
     <row r="14" spans="1:38" s="1" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A14" s="112" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="113"/>
+      <c r="A14" s="100" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="101"/>
       <c r="C14" s="83"/>
       <c r="D14" s="85"/>
       <c r="E14" s="87"/>
       <c r="F14" s="21"/>
       <c r="G14" s="21"/>
       <c r="H14" s="41"/>
-      <c r="I14" s="102"/>
-      <c r="J14" s="103"/>
-      <c r="K14" s="103"/>
-      <c r="L14" s="103"/>
-      <c r="M14" s="103"/>
-      <c r="N14" s="103"/>
-      <c r="O14" s="103"/>
-      <c r="P14" s="103"/>
-      <c r="Q14" s="104"/>
+      <c r="I14" s="153"/>
+      <c r="J14" s="154"/>
+      <c r="K14" s="154"/>
+      <c r="L14" s="154"/>
+      <c r="M14" s="154"/>
+      <c r="N14" s="154"/>
+      <c r="O14" s="154"/>
+      <c r="P14" s="154"/>
+      <c r="Q14" s="155"/>
       <c r="S14"/>
       <c r="T14"/>
       <c r="U14"/>
@@ -2323,25 +2267,25 @@
       <c r="AL14"/>
     </row>
     <row r="15" spans="1:38" s="1" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A15" s="112" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="113"/>
+      <c r="A15" s="100" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="101"/>
       <c r="C15" s="83"/>
       <c r="D15" s="85"/>
       <c r="E15" s="87"/>
       <c r="F15" s="21"/>
       <c r="G15" s="21"/>
       <c r="H15" s="41"/>
-      <c r="I15" s="105"/>
-      <c r="J15" s="106"/>
-      <c r="K15" s="106"/>
-      <c r="L15" s="106"/>
-      <c r="M15" s="106"/>
-      <c r="N15" s="106"/>
-      <c r="O15" s="106"/>
-      <c r="P15" s="106"/>
-      <c r="Q15" s="107"/>
+      <c r="I15" s="156"/>
+      <c r="J15" s="157"/>
+      <c r="K15" s="157"/>
+      <c r="L15" s="157"/>
+      <c r="M15" s="157"/>
+      <c r="N15" s="157"/>
+      <c r="O15" s="157"/>
+      <c r="P15" s="157"/>
+      <c r="Q15" s="158"/>
       <c r="S15"/>
       <c r="T15"/>
       <c r="U15"/>
@@ -2364,25 +2308,25 @@
       <c r="AL15"/>
     </row>
     <row r="16" spans="1:38" s="1" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A16" s="112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="113"/>
+      <c r="A16" s="100" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="101"/>
       <c r="C16" s="83"/>
       <c r="D16" s="85"/>
       <c r="E16" s="87"/>
       <c r="F16" s="21"/>
       <c r="G16" s="21"/>
       <c r="H16" s="41"/>
-      <c r="I16" s="105"/>
-      <c r="J16" s="106"/>
-      <c r="K16" s="106"/>
-      <c r="L16" s="106"/>
-      <c r="M16" s="106"/>
-      <c r="N16" s="106"/>
-      <c r="O16" s="106"/>
-      <c r="P16" s="106"/>
-      <c r="Q16" s="107"/>
+      <c r="I16" s="156"/>
+      <c r="J16" s="157"/>
+      <c r="K16" s="157"/>
+      <c r="L16" s="157"/>
+      <c r="M16" s="157"/>
+      <c r="N16" s="157"/>
+      <c r="O16" s="157"/>
+      <c r="P16" s="157"/>
+      <c r="Q16" s="158"/>
       <c r="S16"/>
       <c r="T16"/>
       <c r="U16"/>
@@ -2405,25 +2349,25 @@
       <c r="AL16"/>
     </row>
     <row r="17" spans="1:38" s="1" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A17" s="112" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" s="113"/>
+      <c r="A17" s="100" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="101"/>
       <c r="C17" s="83"/>
       <c r="D17" s="85"/>
       <c r="E17" s="87"/>
       <c r="F17" s="21"/>
       <c r="G17" s="21"/>
       <c r="H17" s="41"/>
-      <c r="I17" s="105"/>
-      <c r="J17" s="106"/>
-      <c r="K17" s="106"/>
-      <c r="L17" s="106"/>
-      <c r="M17" s="106"/>
-      <c r="N17" s="106"/>
-      <c r="O17" s="106"/>
-      <c r="P17" s="106"/>
-      <c r="Q17" s="107"/>
+      <c r="I17" s="156"/>
+      <c r="J17" s="157"/>
+      <c r="K17" s="157"/>
+      <c r="L17" s="157"/>
+      <c r="M17" s="157"/>
+      <c r="N17" s="157"/>
+      <c r="O17" s="157"/>
+      <c r="P17" s="157"/>
+      <c r="Q17" s="158"/>
       <c r="S17"/>
       <c r="T17"/>
       <c r="U17"/>
@@ -2446,23 +2390,23 @@
       <c r="AL17"/>
     </row>
     <row r="18" spans="1:38" s="1" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A18" s="112"/>
-      <c r="B18" s="113"/>
+      <c r="A18" s="100"/>
+      <c r="B18" s="101"/>
       <c r="C18" s="83"/>
       <c r="D18" s="85"/>
       <c r="E18" s="87"/>
       <c r="F18" s="21"/>
       <c r="G18" s="21"/>
       <c r="H18" s="41"/>
-      <c r="I18" s="105"/>
-      <c r="J18" s="106"/>
-      <c r="K18" s="106"/>
-      <c r="L18" s="106"/>
-      <c r="M18" s="106"/>
-      <c r="N18" s="106"/>
-      <c r="O18" s="106"/>
-      <c r="P18" s="106"/>
-      <c r="Q18" s="107"/>
+      <c r="I18" s="156"/>
+      <c r="J18" s="157"/>
+      <c r="K18" s="157"/>
+      <c r="L18" s="157"/>
+      <c r="M18" s="157"/>
+      <c r="N18" s="157"/>
+      <c r="O18" s="157"/>
+      <c r="P18" s="157"/>
+      <c r="Q18" s="158"/>
       <c r="S18"/>
       <c r="T18"/>
       <c r="U18"/>
@@ -2485,23 +2429,23 @@
       <c r="AL18"/>
     </row>
     <row r="19" spans="1:38" s="1" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A19" s="112"/>
-      <c r="B19" s="113"/>
+      <c r="A19" s="100"/>
+      <c r="B19" s="101"/>
       <c r="C19" s="83"/>
       <c r="D19" s="85"/>
       <c r="E19" s="87"/>
       <c r="F19" s="21"/>
       <c r="G19" s="21"/>
       <c r="H19" s="41"/>
-      <c r="I19" s="105"/>
-      <c r="J19" s="106"/>
-      <c r="K19" s="106"/>
-      <c r="L19" s="106"/>
-      <c r="M19" s="106"/>
-      <c r="N19" s="106"/>
-      <c r="O19" s="106"/>
-      <c r="P19" s="106"/>
-      <c r="Q19" s="107"/>
+      <c r="I19" s="156"/>
+      <c r="J19" s="157"/>
+      <c r="K19" s="157"/>
+      <c r="L19" s="157"/>
+      <c r="M19" s="157"/>
+      <c r="N19" s="157"/>
+      <c r="O19" s="157"/>
+      <c r="P19" s="157"/>
+      <c r="Q19" s="158"/>
       <c r="S19"/>
       <c r="T19"/>
       <c r="U19"/>
@@ -2524,23 +2468,23 @@
       <c r="AL19"/>
     </row>
     <row r="20" spans="1:38" s="1" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A20" s="112"/>
-      <c r="B20" s="113"/>
+      <c r="A20" s="100"/>
+      <c r="B20" s="101"/>
       <c r="C20" s="83"/>
       <c r="D20" s="85"/>
       <c r="E20" s="87"/>
       <c r="F20" s="21"/>
       <c r="G20" s="21"/>
       <c r="H20" s="41"/>
-      <c r="I20" s="105"/>
-      <c r="J20" s="106"/>
-      <c r="K20" s="106"/>
-      <c r="L20" s="106"/>
-      <c r="M20" s="106"/>
-      <c r="N20" s="106"/>
-      <c r="O20" s="106"/>
-      <c r="P20" s="106"/>
-      <c r="Q20" s="107"/>
+      <c r="I20" s="156"/>
+      <c r="J20" s="157"/>
+      <c r="K20" s="157"/>
+      <c r="L20" s="157"/>
+      <c r="M20" s="157"/>
+      <c r="N20" s="157"/>
+      <c r="O20" s="157"/>
+      <c r="P20" s="157"/>
+      <c r="Q20" s="158"/>
       <c r="S20"/>
       <c r="T20"/>
       <c r="U20"/>
@@ -2563,25 +2507,25 @@
       <c r="AL20"/>
     </row>
     <row r="21" spans="1:38" s="1" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A21" s="112" t="s">
-        <v>50</v>
-      </c>
-      <c r="B21" s="113"/>
+      <c r="A21" s="100" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="101"/>
       <c r="C21" s="83"/>
       <c r="D21" s="85"/>
       <c r="E21" s="87"/>
       <c r="F21" s="21"/>
       <c r="G21" s="21"/>
       <c r="H21" s="41"/>
-      <c r="I21" s="105"/>
-      <c r="J21" s="106"/>
-      <c r="K21" s="106"/>
-      <c r="L21" s="106"/>
-      <c r="M21" s="106"/>
-      <c r="N21" s="106"/>
-      <c r="O21" s="106"/>
-      <c r="P21" s="106"/>
-      <c r="Q21" s="107"/>
+      <c r="I21" s="156"/>
+      <c r="J21" s="157"/>
+      <c r="K21" s="157"/>
+      <c r="L21" s="157"/>
+      <c r="M21" s="157"/>
+      <c r="N21" s="157"/>
+      <c r="O21" s="157"/>
+      <c r="P21" s="157"/>
+      <c r="Q21" s="158"/>
       <c r="S21"/>
       <c r="T21"/>
       <c r="U21"/>
@@ -2604,25 +2548,25 @@
       <c r="AL21"/>
     </row>
     <row r="22" spans="1:38" s="1" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A22" s="112" t="s">
-        <v>51</v>
-      </c>
-      <c r="B22" s="113"/>
+      <c r="A22" s="100" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="101"/>
       <c r="C22" s="83"/>
       <c r="D22" s="85"/>
       <c r="E22" s="87"/>
       <c r="F22" s="21"/>
       <c r="G22" s="21"/>
       <c r="H22" s="41"/>
-      <c r="I22" s="105"/>
-      <c r="J22" s="106"/>
-      <c r="K22" s="106"/>
-      <c r="L22" s="106"/>
-      <c r="M22" s="106"/>
-      <c r="N22" s="106"/>
-      <c r="O22" s="106"/>
-      <c r="P22" s="106"/>
-      <c r="Q22" s="107"/>
+      <c r="I22" s="156"/>
+      <c r="J22" s="157"/>
+      <c r="K22" s="157"/>
+      <c r="L22" s="157"/>
+      <c r="M22" s="157"/>
+      <c r="N22" s="157"/>
+      <c r="O22" s="157"/>
+      <c r="P22" s="157"/>
+      <c r="Q22" s="158"/>
       <c r="S22"/>
       <c r="T22"/>
       <c r="U22"/>
@@ -2645,25 +2589,25 @@
       <c r="AL22"/>
     </row>
     <row r="23" spans="1:38" s="1" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A23" s="112" t="s">
-        <v>52</v>
-      </c>
-      <c r="B23" s="113"/>
+      <c r="A23" s="100" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="101"/>
       <c r="C23" s="83"/>
       <c r="D23" s="85"/>
       <c r="E23" s="87"/>
       <c r="F23" s="21"/>
       <c r="G23" s="21"/>
       <c r="H23" s="41"/>
-      <c r="I23" s="105"/>
-      <c r="J23" s="106"/>
-      <c r="K23" s="106"/>
-      <c r="L23" s="106"/>
-      <c r="M23" s="106"/>
-      <c r="N23" s="106"/>
-      <c r="O23" s="106"/>
-      <c r="P23" s="106"/>
-      <c r="Q23" s="107"/>
+      <c r="I23" s="156"/>
+      <c r="J23" s="157"/>
+      <c r="K23" s="157"/>
+      <c r="L23" s="157"/>
+      <c r="M23" s="157"/>
+      <c r="N23" s="157"/>
+      <c r="O23" s="157"/>
+      <c r="P23" s="157"/>
+      <c r="Q23" s="158"/>
       <c r="S23"/>
       <c r="T23"/>
       <c r="U23"/>
@@ -2686,25 +2630,25 @@
       <c r="AL23"/>
     </row>
     <row r="24" spans="1:38" s="1" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A24" s="112" t="s">
-        <v>53</v>
-      </c>
-      <c r="B24" s="113"/>
+      <c r="A24" s="100" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="101"/>
       <c r="C24" s="83"/>
       <c r="D24" s="85"/>
       <c r="E24" s="87"/>
       <c r="F24" s="21"/>
       <c r="G24" s="21"/>
       <c r="H24" s="41"/>
-      <c r="I24" s="105"/>
-      <c r="J24" s="106"/>
-      <c r="K24" s="106"/>
-      <c r="L24" s="106"/>
-      <c r="M24" s="106"/>
-      <c r="N24" s="106"/>
-      <c r="O24" s="106"/>
-      <c r="P24" s="106"/>
-      <c r="Q24" s="107"/>
+      <c r="I24" s="156"/>
+      <c r="J24" s="157"/>
+      <c r="K24" s="157"/>
+      <c r="L24" s="157"/>
+      <c r="M24" s="157"/>
+      <c r="N24" s="157"/>
+      <c r="O24" s="157"/>
+      <c r="P24" s="157"/>
+      <c r="Q24" s="158"/>
       <c r="S24"/>
       <c r="T24"/>
       <c r="U24"/>
@@ -2727,25 +2671,25 @@
       <c r="AL24"/>
     </row>
     <row r="25" spans="1:38" s="1" customFormat="1" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A25" s="112" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25" s="113"/>
+      <c r="A25" s="100" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="101"/>
       <c r="C25" s="83"/>
       <c r="D25" s="85"/>
       <c r="E25" s="87"/>
       <c r="F25" s="21"/>
       <c r="G25" s="21"/>
       <c r="H25" s="41"/>
-      <c r="I25" s="108"/>
-      <c r="J25" s="109"/>
-      <c r="K25" s="109"/>
-      <c r="L25" s="109"/>
-      <c r="M25" s="109"/>
-      <c r="N25" s="109"/>
-      <c r="O25" s="109"/>
-      <c r="P25" s="109"/>
-      <c r="Q25" s="110"/>
+      <c r="I25" s="159"/>
+      <c r="J25" s="160"/>
+      <c r="K25" s="160"/>
+      <c r="L25" s="160"/>
+      <c r="M25" s="160"/>
+      <c r="N25" s="160"/>
+      <c r="O25" s="160"/>
+      <c r="P25" s="160"/>
+      <c r="Q25" s="161"/>
       <c r="S25"/>
       <c r="T25"/>
       <c r="U25"/>
@@ -2768,27 +2712,27 @@
       <c r="AL25"/>
     </row>
     <row r="26" spans="1:38" s="1" customFormat="1" ht="19.5" customHeight="1" thickTop="1">
-      <c r="A26" s="112" t="s">
-        <v>56</v>
-      </c>
-      <c r="B26" s="113"/>
+      <c r="A26" s="100" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" s="101"/>
       <c r="C26" s="83"/>
       <c r="D26" s="85"/>
       <c r="E26" s="87"/>
       <c r="F26" s="21"/>
       <c r="G26" s="21"/>
       <c r="H26" s="41"/>
-      <c r="I26" s="162" t="s">
-        <v>16</v>
-      </c>
-      <c r="J26" s="162"/>
-      <c r="K26" s="162"/>
-      <c r="L26" s="162"/>
-      <c r="M26" s="162"/>
-      <c r="N26" s="162"/>
-      <c r="O26" s="162"/>
-      <c r="P26" s="162"/>
-      <c r="Q26" s="162"/>
+      <c r="I26" s="99" t="s">
+        <v>15</v>
+      </c>
+      <c r="J26" s="99"/>
+      <c r="K26" s="99"/>
+      <c r="L26" s="99"/>
+      <c r="M26" s="99"/>
+      <c r="N26" s="99"/>
+      <c r="O26" s="99"/>
+      <c r="P26" s="99"/>
+      <c r="Q26" s="99"/>
       <c r="S26"/>
       <c r="T26"/>
       <c r="U26"/>
@@ -2811,30 +2755,30 @@
       <c r="AL26"/>
     </row>
     <row r="27" spans="1:38" s="1" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A27" s="112"/>
-      <c r="B27" s="113"/>
+      <c r="A27" s="100"/>
+      <c r="B27" s="101"/>
       <c r="C27" s="83"/>
       <c r="D27" s="85"/>
       <c r="E27" s="87"/>
       <c r="F27" s="21"/>
       <c r="G27" s="21"/>
       <c r="H27" s="41"/>
-      <c r="I27" s="152" t="s">
+      <c r="I27" s="106" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="106"/>
+      <c r="K27" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="J27" s="152"/>
-      <c r="K27" s="152" t="s">
+      <c r="L27" s="106"/>
+      <c r="M27" s="106"/>
+      <c r="N27" s="106"/>
+      <c r="O27" s="106"/>
+      <c r="P27" s="95" t="s">
         <v>18</v>
       </c>
-      <c r="L27" s="152"/>
-      <c r="M27" s="152"/>
-      <c r="N27" s="152"/>
-      <c r="O27" s="152"/>
-      <c r="P27" s="95" t="s">
+      <c r="Q27" s="95" t="s">
         <v>19</v>
-      </c>
-      <c r="Q27" s="95" t="s">
-        <v>20</v>
       </c>
       <c r="S27"/>
       <c r="T27"/>
@@ -2858,21 +2802,21 @@
       <c r="AL27"/>
     </row>
     <row r="28" spans="1:38" s="1" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A28" s="112"/>
-      <c r="B28" s="113"/>
+      <c r="A28" s="100"/>
+      <c r="B28" s="101"/>
       <c r="C28" s="83"/>
       <c r="D28" s="85"/>
       <c r="E28" s="87"/>
       <c r="F28" s="21"/>
       <c r="G28" s="21"/>
       <c r="H28" s="41"/>
-      <c r="I28" s="151"/>
-      <c r="J28" s="151"/>
-      <c r="K28" s="151"/>
-      <c r="L28" s="151"/>
-      <c r="M28" s="151"/>
-      <c r="N28" s="151"/>
-      <c r="O28" s="151"/>
+      <c r="I28" s="104"/>
+      <c r="J28" s="104"/>
+      <c r="K28" s="104"/>
+      <c r="L28" s="104"/>
+      <c r="M28" s="104"/>
+      <c r="N28" s="104"/>
+      <c r="O28" s="104"/>
       <c r="P28" s="51"/>
       <c r="Q28" s="50"/>
       <c r="S28"/>
@@ -2897,21 +2841,21 @@
       <c r="AL28"/>
     </row>
     <row r="29" spans="1:38" s="1" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A29" s="112"/>
-      <c r="B29" s="113"/>
+      <c r="A29" s="100"/>
+      <c r="B29" s="101"/>
       <c r="C29" s="83"/>
       <c r="D29" s="85"/>
       <c r="E29" s="87"/>
       <c r="F29" s="21"/>
       <c r="G29" s="21"/>
       <c r="H29" s="41"/>
-      <c r="I29" s="153"/>
-      <c r="J29" s="153"/>
-      <c r="K29" s="153"/>
-      <c r="L29" s="153"/>
-      <c r="M29" s="153"/>
-      <c r="N29" s="153"/>
-      <c r="O29" s="153"/>
+      <c r="I29" s="103"/>
+      <c r="J29" s="103"/>
+      <c r="K29" s="103"/>
+      <c r="L29" s="103"/>
+      <c r="M29" s="103"/>
+      <c r="N29" s="103"/>
+      <c r="O29" s="103"/>
       <c r="P29" s="93"/>
       <c r="Q29" s="93"/>
       <c r="S29"/>
@@ -2936,21 +2880,21 @@
       <c r="AL29"/>
     </row>
     <row r="30" spans="1:38" s="1" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A30" s="112"/>
-      <c r="B30" s="113"/>
+      <c r="A30" s="100"/>
+      <c r="B30" s="101"/>
       <c r="C30" s="83"/>
       <c r="D30" s="85"/>
       <c r="E30" s="87"/>
       <c r="F30" s="21"/>
       <c r="G30" s="21"/>
       <c r="H30" s="41"/>
-      <c r="I30" s="151"/>
-      <c r="J30" s="151"/>
-      <c r="K30" s="151"/>
-      <c r="L30" s="151"/>
-      <c r="M30" s="151"/>
-      <c r="N30" s="151"/>
-      <c r="O30" s="151"/>
+      <c r="I30" s="104"/>
+      <c r="J30" s="104"/>
+      <c r="K30" s="104"/>
+      <c r="L30" s="104"/>
+      <c r="M30" s="104"/>
+      <c r="N30" s="104"/>
+      <c r="O30" s="104"/>
       <c r="P30" s="50"/>
       <c r="Q30" s="50"/>
       <c r="S30"/>
@@ -2975,21 +2919,21 @@
       <c r="AL30"/>
     </row>
     <row r="31" spans="1:38" s="1" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A31" s="112"/>
-      <c r="B31" s="113"/>
+      <c r="A31" s="100"/>
+      <c r="B31" s="101"/>
       <c r="C31" s="83"/>
       <c r="D31" s="85"/>
       <c r="E31" s="87"/>
       <c r="F31" s="21"/>
       <c r="G31" s="21"/>
       <c r="H31" s="41"/>
-      <c r="I31" s="153"/>
-      <c r="J31" s="153"/>
-      <c r="K31" s="153"/>
-      <c r="L31" s="153"/>
-      <c r="M31" s="153"/>
-      <c r="N31" s="153"/>
-      <c r="O31" s="153"/>
+      <c r="I31" s="103"/>
+      <c r="J31" s="103"/>
+      <c r="K31" s="103"/>
+      <c r="L31" s="103"/>
+      <c r="M31" s="103"/>
+      <c r="N31" s="103"/>
+      <c r="O31" s="103"/>
       <c r="P31" s="93"/>
       <c r="Q31" s="93"/>
       <c r="S31"/>
@@ -3014,21 +2958,21 @@
       <c r="AL31"/>
     </row>
     <row r="32" spans="1:38" s="1" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A32" s="112"/>
-      <c r="B32" s="113"/>
+      <c r="A32" s="100"/>
+      <c r="B32" s="101"/>
       <c r="C32" s="83"/>
       <c r="D32" s="85"/>
       <c r="E32" s="87"/>
       <c r="F32" s="21"/>
       <c r="G32" s="21"/>
       <c r="H32" s="41"/>
-      <c r="I32" s="151"/>
-      <c r="J32" s="151"/>
-      <c r="K32" s="151"/>
-      <c r="L32" s="151"/>
-      <c r="M32" s="151"/>
-      <c r="N32" s="151"/>
-      <c r="O32" s="151"/>
+      <c r="I32" s="104"/>
+      <c r="J32" s="104"/>
+      <c r="K32" s="104"/>
+      <c r="L32" s="104"/>
+      <c r="M32" s="104"/>
+      <c r="N32" s="104"/>
+      <c r="O32" s="104"/>
       <c r="P32" s="50"/>
       <c r="Q32" s="50"/>
       <c r="S32"/>
@@ -3053,21 +2997,21 @@
       <c r="AL32"/>
     </row>
     <row r="33" spans="1:38" s="1" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A33" s="114"/>
-      <c r="B33" s="115"/>
+      <c r="A33" s="162"/>
+      <c r="B33" s="163"/>
       <c r="C33" s="84"/>
       <c r="D33" s="86"/>
       <c r="E33" s="24"/>
       <c r="F33" s="24"/>
       <c r="G33" s="24"/>
       <c r="H33" s="42"/>
-      <c r="I33" s="150"/>
-      <c r="J33" s="150"/>
-      <c r="K33" s="163"/>
-      <c r="L33" s="163"/>
-      <c r="M33" s="163"/>
-      <c r="N33" s="163"/>
-      <c r="O33" s="163"/>
+      <c r="I33" s="113"/>
+      <c r="J33" s="113"/>
+      <c r="K33" s="105"/>
+      <c r="L33" s="105"/>
+      <c r="M33" s="105"/>
+      <c r="N33" s="105"/>
+      <c r="O33" s="105"/>
       <c r="P33" s="94"/>
       <c r="Q33" s="94"/>
       <c r="S33"/>
@@ -3093,7 +3037,7 @@
     </row>
     <row r="34" spans="1:38" s="18" customFormat="1" ht="11.25" customHeight="1" thickTop="1">
       <c r="A34" s="25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B34" s="26"/>
       <c r="C34" s="25"/>
@@ -3103,7 +3047,7 @@
       <c r="G34" s="25"/>
       <c r="H34" s="28"/>
       <c r="I34" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J34" s="26"/>
       <c r="K34" s="26"/>
@@ -3135,21 +3079,21 @@
       <c r="AL34"/>
     </row>
     <row r="35" spans="1:38" s="3" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="A35" s="111"/>
-      <c r="B35" s="111"/>
-      <c r="C35" s="161"/>
-      <c r="D35" s="161"/>
+      <c r="A35" s="102"/>
+      <c r="B35" s="102"/>
+      <c r="C35" s="98"/>
+      <c r="D35" s="98"/>
       <c r="E35" s="30"/>
-      <c r="F35" s="161"/>
-      <c r="G35" s="161"/>
+      <c r="F35" s="98"/>
+      <c r="G35" s="98"/>
       <c r="H35" s="31"/>
-      <c r="I35" s="111"/>
-      <c r="J35" s="111"/>
-      <c r="K35" s="111"/>
-      <c r="L35" s="111"/>
-      <c r="M35" s="111"/>
-      <c r="N35" s="111"/>
-      <c r="O35" s="111"/>
+      <c r="I35" s="102"/>
+      <c r="J35" s="102"/>
+      <c r="K35" s="102"/>
+      <c r="L35" s="102"/>
+      <c r="M35" s="102"/>
+      <c r="N35" s="102"/>
+      <c r="O35" s="102"/>
       <c r="P35" s="34"/>
       <c r="Q35" s="34"/>
       <c r="S35"/>
@@ -3175,7 +3119,7 @@
     </row>
     <row r="36" spans="1:38" s="3" customFormat="1" ht="11.25" customHeight="1" thickTop="1">
       <c r="A36" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="13"/>
@@ -3185,7 +3129,7 @@
       <c r="G36" s="8"/>
       <c r="H36" s="8"/>
       <c r="I36" s="23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J36" s="17"/>
       <c r="K36" s="17"/>
@@ -3216,8 +3160,8 @@
       <c r="AL36"/>
     </row>
     <row r="37" spans="1:38" s="3" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="A37" s="156"/>
-      <c r="B37" s="156"/>
+      <c r="A37" s="97"/>
+      <c r="B37" s="97"/>
       <c r="C37" s="36"/>
       <c r="D37" s="31"/>
       <c r="E37" s="37"/>
@@ -3226,11 +3170,11 @@
       <c r="H37" s="37"/>
       <c r="I37" s="90"/>
       <c r="J37" s="33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K37" s="32"/>
       <c r="L37" s="33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M37" s="34"/>
       <c r="N37" s="34"/>
@@ -3262,26 +3206,26 @@
       <c r="A38" s="7"/>
       <c r="B38" s="6"/>
       <c r="C38" s="25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D38" s="27"/>
       <c r="E38" s="27"/>
       <c r="F38" s="25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G38" s="25"/>
       <c r="H38" s="8"/>
-      <c r="I38" s="157" t="s">
+      <c r="I38" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="J38" s="157"/>
-      <c r="K38" s="157"/>
-      <c r="L38" s="157"/>
-      <c r="M38" s="159" t="s">
-        <v>29</v>
-      </c>
-      <c r="N38" s="159"/>
-      <c r="O38" s="159"/>
+      <c r="J38" s="109"/>
+      <c r="K38" s="109"/>
+      <c r="L38" s="109"/>
+      <c r="M38" s="111" t="s">
+        <v>28</v>
+      </c>
+      <c r="N38" s="111"/>
+      <c r="O38" s="111"/>
       <c r="P38" s="15"/>
       <c r="S38"/>
       <c r="T38"/>
@@ -3307,19 +3251,19 @@
     <row r="39" spans="1:38" s="3" customFormat="1" ht="15" customHeight="1" thickBot="1">
       <c r="A39" s="37"/>
       <c r="B39" s="37"/>
-      <c r="C39" s="160"/>
-      <c r="D39" s="160"/>
+      <c r="C39" s="112"/>
+      <c r="D39" s="112"/>
       <c r="E39" s="88"/>
-      <c r="F39" s="160"/>
-      <c r="G39" s="160"/>
+      <c r="F39" s="112"/>
+      <c r="G39" s="112"/>
       <c r="H39" s="48"/>
-      <c r="I39" s="156"/>
-      <c r="J39" s="156"/>
-      <c r="K39" s="156"/>
-      <c r="L39" s="156"/>
-      <c r="M39" s="154"/>
-      <c r="N39" s="155"/>
-      <c r="O39" s="155"/>
+      <c r="I39" s="97"/>
+      <c r="J39" s="97"/>
+      <c r="K39" s="97"/>
+      <c r="L39" s="97"/>
+      <c r="M39" s="107"/>
+      <c r="N39" s="108"/>
+      <c r="O39" s="108"/>
       <c r="P39" s="38"/>
       <c r="Q39" s="40"/>
       <c r="S39"/>
@@ -3345,30 +3289,30 @@
     </row>
     <row r="40" spans="1:38" s="3" customFormat="1" ht="11.25" customHeight="1" thickTop="1">
       <c r="A40" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
       <c r="F40" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G40" s="8"/>
       <c r="H40" s="8"/>
-      <c r="I40" s="157" t="s">
+      <c r="I40" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="J40" s="157"/>
-      <c r="K40" s="157"/>
-      <c r="L40" s="157"/>
-      <c r="M40" s="159" t="s">
-        <v>29</v>
-      </c>
-      <c r="N40" s="159"/>
-      <c r="O40" s="159"/>
+      <c r="J40" s="109"/>
+      <c r="K40" s="109"/>
+      <c r="L40" s="109"/>
+      <c r="M40" s="111" t="s">
+        <v>28</v>
+      </c>
+      <c r="N40" s="111"/>
+      <c r="O40" s="111"/>
       <c r="P40" s="15"/>
       <c r="S40"/>
       <c r="T40"/>
@@ -3392,27 +3336,25 @@
       <c r="AL40"/>
     </row>
     <row r="41" spans="1:38" s="3" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="A41" s="156"/>
-      <c r="B41" s="156"/>
+      <c r="A41" s="97"/>
+      <c r="B41" s="97"/>
       <c r="C41" s="46" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D41" s="89"/>
       <c r="E41" s="47" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F41" s="89"/>
       <c r="G41" s="31"/>
       <c r="H41" s="31"/>
-      <c r="I41" s="158" t="s">
-        <v>9</v>
-      </c>
-      <c r="J41" s="158"/>
-      <c r="K41" s="158"/>
-      <c r="L41" s="158"/>
-      <c r="M41" s="154"/>
-      <c r="N41" s="155"/>
-      <c r="O41" s="155"/>
+      <c r="I41" s="110"/>
+      <c r="J41" s="110"/>
+      <c r="K41" s="110"/>
+      <c r="L41" s="110"/>
+      <c r="M41" s="107"/>
+      <c r="N41" s="108"/>
+      <c r="O41" s="108"/>
       <c r="P41" s="38"/>
       <c r="Q41" s="39"/>
       <c r="S41"/>
@@ -3436,18 +3378,82 @@
       <c r="AK41"/>
       <c r="AL41"/>
     </row>
-    <row r="42" spans="1:38" ht="13" thickTop="1">
+    <row r="42" spans="1:38" ht="13.8" thickTop="1">
       <c r="D42" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45" spans="1:38">
       <c r="O45" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="80">
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:Q12"/>
+    <mergeCell ref="I14:Q25"/>
+    <mergeCell ref="I35:O35"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="G5:G11"/>
+    <mergeCell ref="H5:H11"/>
+    <mergeCell ref="C5:C11"/>
+    <mergeCell ref="D5:D11"/>
+    <mergeCell ref="E5:E11"/>
+    <mergeCell ref="F5:F11"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K6:O6"/>
+    <mergeCell ref="K7:O7"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="A1:Q2"/>
+    <mergeCell ref="C3:N3"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:O5"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="K28:O28"/>
+    <mergeCell ref="K27:O27"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="M41:O41"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="I41:L41"/>
+    <mergeCell ref="M38:O38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="M39:O39"/>
+    <mergeCell ref="M40:O40"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="F35:G35"/>
     <mergeCell ref="C35:D35"/>
@@ -3464,70 +3470,6 @@
     <mergeCell ref="I27:J27"/>
     <mergeCell ref="K30:O30"/>
     <mergeCell ref="K29:O29"/>
-    <mergeCell ref="M41:O41"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="I40:L40"/>
-    <mergeCell ref="I41:L41"/>
-    <mergeCell ref="M38:O38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="M39:O39"/>
-    <mergeCell ref="M40:O40"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="K28:O28"/>
-    <mergeCell ref="K27:O27"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:O6"/>
-    <mergeCell ref="K7:O7"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="A1:Q2"/>
-    <mergeCell ref="C3:N3"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:O5"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="G5:G11"/>
-    <mergeCell ref="H5:H11"/>
-    <mergeCell ref="C5:C11"/>
-    <mergeCell ref="D5:D11"/>
-    <mergeCell ref="E5:E11"/>
-    <mergeCell ref="F5:F11"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:Q12"/>
-    <mergeCell ref="I14:Q25"/>
-    <mergeCell ref="I35:O35"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -3545,20 +3487,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AMJ63"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="6" width="10.7265625" style="55" customWidth="1"/>
-    <col min="7" max="7" width="1.26953125" style="55" customWidth="1"/>
-    <col min="8" max="256" width="10.7265625" style="55" customWidth="1"/>
-    <col min="257" max="257" width="11.453125" style="54" customWidth="1"/>
-    <col min="258" max="1024" width="8.81640625" style="54" customWidth="1"/>
-    <col min="1025" max="1025" width="10.26953125" style="53" customWidth="1"/>
-    <col min="1026" max="16384" width="9.1796875" style="53"/>
+    <col min="1" max="6" width="10.77734375" style="55" customWidth="1"/>
+    <col min="7" max="7" width="1.21875" style="55" customWidth="1"/>
+    <col min="8" max="256" width="10.77734375" style="55" customWidth="1"/>
+    <col min="257" max="257" width="11.44140625" style="54" customWidth="1"/>
+    <col min="258" max="1024" width="8.77734375" style="54" customWidth="1"/>
+    <col min="1025" max="1025" width="10.21875" style="53" customWidth="1"/>
+    <col min="1026" max="16384" width="9.21875" style="53"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" s="55" customFormat="1">
       <c r="A1" s="164" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B1" s="164"/>
       <c r="C1" s="164"/>
@@ -3579,25 +3521,19 @@
     </row>
     <row r="3" spans="1:19" s="55" customFormat="1">
       <c r="A3" s="66" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="171">
-        <f>'Daily Work Report'!Q5</f>
-        <v>0</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B3" s="171"/>
       <c r="C3" s="171"/>
       <c r="D3" s="72"/>
       <c r="E3" s="73"/>
       <c r="F3" s="73"/>
       <c r="G3" s="65"/>
       <c r="H3" s="72" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I3" s="65"/>
-      <c r="J3" s="173" t="str">
-        <f>'Daily Work Report'!B5</f>
-        <v>439</v>
-      </c>
+      <c r="J3" s="173"/>
       <c r="K3" s="173"/>
       <c r="L3" s="173"/>
       <c r="M3" s="69"/>
@@ -3619,13 +3555,10 @@
     </row>
     <row r="5" spans="1:19" s="55" customFormat="1">
       <c r="A5" s="66" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B5" s="65"/>
-      <c r="C5" s="174" t="str">
-        <f>'Daily Work Report'!B7</f>
-        <v>PAVEMENT MARKING OF BRIDGE DECK AND ROADWAY</v>
-      </c>
+      <c r="C5" s="174"/>
       <c r="D5" s="174"/>
       <c r="E5" s="174"/>
       <c r="F5" s="174"/>
@@ -3643,12 +3576,10 @@
     </row>
     <row r="7" spans="1:19" s="55" customFormat="1">
       <c r="A7" s="66" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B7" s="65"/>
-      <c r="C7" s="172" t="s">
-        <v>9</v>
-      </c>
+      <c r="C7" s="172"/>
       <c r="D7" s="172"/>
       <c r="E7" s="172"/>
       <c r="F7" s="172"/>
@@ -3660,14 +3591,14 @@
       <c r="L7" s="172"/>
       <c r="M7" s="172"/>
     </row>
-    <row r="8" spans="1:19" s="55" customFormat="1" ht="14.5" thickBot="1">
+    <row r="8" spans="1:19" s="55" customFormat="1" ht="14.4" thickBot="1">
       <c r="A8" s="61"/>
       <c r="L8" s="64"/>
       <c r="M8" s="60"/>
     </row>
     <row r="9" spans="1:19" s="55" customFormat="1">
       <c r="A9" s="164" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B9" s="164"/>
       <c r="C9" s="164"/>
@@ -3676,7 +3607,7 @@
       <c r="F9" s="164"/>
       <c r="G9" s="59"/>
       <c r="H9" s="164" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I9" s="164"/>
       <c r="J9" s="164"/>
@@ -3729,7 +3660,7 @@
       <c r="L12" s="166"/>
       <c r="M12" s="167"/>
     </row>
-    <row r="13" spans="1:19" s="55" customFormat="1" ht="14.5">
+    <row r="13" spans="1:19" s="55" customFormat="1" ht="14.4">
       <c r="A13" s="165"/>
       <c r="B13" s="166"/>
       <c r="C13" s="166"/>
@@ -3745,7 +3676,7 @@
       <c r="M13" s="167"/>
       <c r="P13" s="62"/>
       <c r="Q13" s="55" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:19" s="55" customFormat="1">
@@ -3794,7 +3725,7 @@
       <c r="M16" s="167"/>
       <c r="S16" s="63"/>
     </row>
-    <row r="17" spans="1:17" s="55" customFormat="1" ht="14.5">
+    <row r="17" spans="1:17" s="55" customFormat="1" ht="14.4">
       <c r="A17" s="165"/>
       <c r="B17" s="166"/>
       <c r="C17" s="166"/>
@@ -3825,7 +3756,7 @@
       <c r="L18" s="166"/>
       <c r="M18" s="167"/>
     </row>
-    <row r="19" spans="1:17" s="55" customFormat="1" ht="14.5">
+    <row r="19" spans="1:17" s="55" customFormat="1" ht="14.4">
       <c r="A19" s="165"/>
       <c r="B19" s="166"/>
       <c r="C19" s="166"/>
@@ -3842,7 +3773,7 @@
       <c r="P19" s="62"/>
       <c r="Q19" s="63"/>
     </row>
-    <row r="20" spans="1:17" s="55" customFormat="1" ht="14.5">
+    <row r="20" spans="1:17" s="55" customFormat="1" ht="14.4">
       <c r="A20" s="165"/>
       <c r="B20" s="166"/>
       <c r="C20" s="166"/>
@@ -3918,7 +3849,7 @@
       <c r="L24" s="166"/>
       <c r="M24" s="167"/>
     </row>
-    <row r="25" spans="1:17" s="55" customFormat="1" ht="14.5" customHeight="1" thickBot="1">
+    <row r="25" spans="1:17" s="55" customFormat="1" ht="14.55" customHeight="1" thickBot="1">
       <c r="A25" s="168"/>
       <c r="B25" s="169"/>
       <c r="C25" s="169"/>
@@ -3940,7 +3871,7 @@
     </row>
     <row r="27" spans="1:17" s="55" customFormat="1">
       <c r="A27" s="164" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B27" s="164"/>
       <c r="C27" s="164"/>
@@ -3949,7 +3880,7 @@
       <c r="F27" s="164"/>
       <c r="G27" s="59"/>
       <c r="H27" s="164" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I27" s="164"/>
       <c r="J27" s="164"/>
@@ -4182,7 +4113,7 @@
       <c r="L42" s="166"/>
       <c r="M42" s="167"/>
     </row>
-    <row r="43" spans="1:13" s="55" customFormat="1" ht="14.5" customHeight="1" thickBot="1">
+    <row r="43" spans="1:13" s="55" customFormat="1" ht="14.55" customHeight="1" thickBot="1">
       <c r="A43" s="168"/>
       <c r="B43" s="169"/>
       <c r="C43" s="169"/>
@@ -4203,7 +4134,7 @@
     </row>
     <row r="45" spans="1:13" s="55" customFormat="1" ht="15" customHeight="1">
       <c r="A45" s="164" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B45" s="164"/>
       <c r="C45" s="164"/>
@@ -4212,7 +4143,7 @@
       <c r="F45" s="164"/>
       <c r="G45" s="59"/>
       <c r="H45" s="164" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I45" s="164"/>
       <c r="J45" s="164"/>
@@ -4445,7 +4376,7 @@
       <c r="L60" s="166"/>
       <c r="M60" s="167"/>
     </row>
-    <row r="61" spans="1:13" s="55" customFormat="1" ht="14.5" customHeight="1" thickBot="1">
+    <row r="61" spans="1:13" s="55" customFormat="1" ht="14.55" customHeight="1" thickBot="1">
       <c r="A61" s="168"/>
       <c r="B61" s="169"/>
       <c r="C61" s="169"/>
@@ -4464,12 +4395,6 @@
     <row r="63" spans="1:13" s="55" customFormat="1"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="A28:F43"/>
-    <mergeCell ref="H28:M43"/>
-    <mergeCell ref="A46:F61"/>
-    <mergeCell ref="H46:M61"/>
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="H27:M27"/>
     <mergeCell ref="A10:F25"/>
@@ -4481,6 +4406,12 @@
     <mergeCell ref="H9:M9"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="C5:M5"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="A28:F43"/>
+    <mergeCell ref="H28:M43"/>
+    <mergeCell ref="A46:F61"/>
+    <mergeCell ref="H46:M61"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4492,6 +4423,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="b4b04b17-0e5b-4f89-894f-b9477d4aa4a7">
@@ -4501,15 +4441,6 @@
     <Comments xmlns="b4b04b17-0e5b-4f89-894f-b9477d4aa4a7" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4762,6 +4693,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1404CCC0-6F9E-4D43-8A00-9868060E1B2C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07E8D94C-70BB-43EF-AF43-1AE54D4D4E56}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="c71a2ab4-081f-40b8-a20a-fa4202923702"/>
@@ -4774,14 +4713,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1404CCC0-6F9E-4D43-8A00-9868060E1B2C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
